--- a/ui_runner/templates/graded_analysis_tabs_2026-05-19.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-19.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>53.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>71.2</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>71.40000000000001</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>46.2</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>30.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>615</v>
+        <v>956</v>
       </c>
       <c r="E8" t="n">
-        <v>152</v>
+        <v>280</v>
       </c>
       <c r="F8" t="n">
-        <v>463</v>
+        <v>676</v>
       </c>
       <c r="G8" t="n">
-        <v>24.7</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>51</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="E10" t="n">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="F10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="G10" t="n">
-        <v>66.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G11" t="n">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>62.9</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>85</v>
+        <v>434</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>236</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>198</v>
       </c>
       <c r="G13" t="n">
-        <v>63.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="G15" t="n">
-        <v>25.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2642</v>
+        <v>3349</v>
       </c>
       <c r="E17" t="n">
-        <v>573</v>
+        <v>686</v>
       </c>
       <c r="F17" t="n">
-        <v>2069</v>
+        <v>2663</v>
       </c>
       <c r="G17" t="n">
-        <v>21.7</v>
+        <v>20.5</v>
       </c>
     </row>
   </sheetData>
@@ -1106,73 +1106,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78.8</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2" t="n">
-        <v>73.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
-        <v>60.7</v>
+        <v>60</v>
       </c>
       <c r="I2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>40</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
         <v>100</v>
       </c>
-      <c r="M2" t="n">
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W2" t="n">
         <v>3</v>
       </c>
-      <c r="P2" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>42</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>26.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>260</v>
+        <v>355</v>
       </c>
       <c r="Z2" t="n">
         <v>100</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
         <v>60</v>
@@ -1187,10 +1193,10 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>57.1</v>
+        <v>35.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1199,14 +1205,23 @@
           <t>Above Avg</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1214,17 +1229,26 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
+      <c r="R3" t="n">
+        <v>100</v>
+      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1233,22 +1257,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>102</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
+      <c r="AF3" t="n">
+        <v>37.5</v>
+      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1270,40 +1300,28 @@
         <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>63.4</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>35.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1318,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="n">
         <v>100</v>
@@ -1342,10 +1360,10 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>53.2</v>
+        <v>54.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -1403,22 +1421,25 @@
         <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>44.4</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>50</v>
+      </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>18.2</v>
+        <v>20.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1426,20 +1447,20 @@
       <c r="AA5" t="n">
         <v>2</v>
       </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
       <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1497,43 +1518,49 @@
         <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>78.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>50</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
         <v>100</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>57.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>46.2</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -1543,100 +1570,100 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="D7" t="n">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="E7" t="n">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="F7" t="n">
-        <v>62.9</v>
+        <v>60.9</v>
       </c>
       <c r="G7" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H7" t="n">
-        <v>63.5</v>
+        <v>54.4</v>
       </c>
       <c r="I7" t="n">
-        <v>85</v>
+        <v>434</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="K7" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L7" t="n">
-        <v>25.8</v>
+        <v>22.7</v>
       </c>
       <c r="M7" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="N7" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="O7" t="n">
+        <v>58</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3349</v>
+      </c>
+      <c r="R7" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>38</v>
+      </c>
+      <c r="X7" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>956</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AA7" t="n">
         <v>56</v>
       </c>
-      <c r="P7" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2642</v>
-      </c>
-      <c r="R7" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>28</v>
-      </c>
-      <c r="T7" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26</v>
-      </c>
-      <c r="X7" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>615</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AC7" t="n">
         <v>52</v>
       </c>
-      <c r="AB7" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>42</v>
-      </c>
       <c r="AD7" t="n">
-        <v>30.6</v>
+        <v>45.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>51</v>
+        <v>42.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>102</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
